--- a/نموذج الجرد الخاص بالديغما.xlsx
+++ b/نموذج الجرد الخاص بالديغما.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC2C051-B768-43C5-836F-34794102444C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD08586-BEAA-4057-938C-FC561C625E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8B99DF13-446F-4445-87FD-30D12854ABEC}"/>
   </bookViews>
@@ -488,160 +488,126 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="37.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="80.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
